--- a/tests/fixtures/simple-ok.xlsx
+++ b/tests/fixtures/simple-ok.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品リスト" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="シーン設定" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,30 +425,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>メーカー</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>分類</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>価格(円)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TAISコード</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>ひとこと説明</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>仕様</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>困りごと1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>困りごと2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>誰が使う</t>
         </is>
@@ -461,28 +477,44 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>あおぞら福祉機器</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>歩行補助</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1200</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>01234-000001</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>軽くてにぎりやすい定番の一本杖</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>重さ:290g
+高さ調節:71〜94cm(10段階)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>ふらつく・転びやすい</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>屋外の外出が不安</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>本人が使う</t>
         </is>
@@ -494,30 +526,38 @@
           <t>ささえ四点杖ワイド</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>歩行補助</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>1800</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>自立するから立ち上がり時も支えになる四点杖</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>重さ:640g
+高さ調節:66〜89cm</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>ふらつく・転びやすい</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>支えがないと立てない</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>本人が使う</t>
         </is>
@@ -531,30 +571,435 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>みらいケア</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>見守り・生活サポート</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>2000</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>夜中の動きをやさしく知らせる見守りセンサー</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>夜中に動き回る</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>一人にするのが心配</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>どちらも</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>場面</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>困りごと</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>歩く・移動</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ふらつく・転びやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>歩く・移動</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>長い距離を歩けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>歩く・移動</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>屋外の外出が不安</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>歩く・移動</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>段差につまずく</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>歩く・移動</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>荷物を持って歩けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>立つ・座る</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>立ち上がるのがつらい</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>立つ・座る</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>座るときにドスンと落ちる</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>立つ・座る</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ひざ・腰が痛い</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>立つ・座る</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>支えがないと立てない</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>寝る・起きる</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>起き上がれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>寝る・起きる</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ベッドから立ち上がれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>寝る・起きる</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>寝返りが打てない</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>寝る・起きる</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>床ずれが心配</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>寝る・起きる</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>布団の上げ下ろしがつらい</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>お風呂</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>浴槽をまたぐのがこわい</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>お風呂</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>浴室で立ち上がれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>お風呂</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>滑るのが心配</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>お風呂</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>体を洗いにくい</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>お風呂</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>浴室まで移動できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>トイレ</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>トイレまで間に合わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>トイレ</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>便座から立ち上がれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>トイレ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>夜のトイレが不安</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>トイレ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>トイレまで移動できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>食事</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>箸・スプーンが持ちにくい</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>食事</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>食器が滑る・こぼす</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>食事</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>姿勢を保てない</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>食事</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>飲み込みが心配</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>見守り・その他</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>一人にするのが心配</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>見守り・その他</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>夜中に動き回る</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>見守り・その他</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>呼ばれてもすぐ行けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>見守り・その他</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>介助者の負担が大きい</t>
         </is>
       </c>
     </row>
